--- a/ecosysem/db/Excels/DeltaH0f.xlsx
+++ b/ecosysem/db/Excels/DeltaH0f.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\db\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4292844A-EC27-49BE-9BDA-C2C82DE4BCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FE3161-AC51-4065-B98A-6FE646B22F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
   </bookViews>
   <sheets>
     <sheet name="DeltaH" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="91">
   <si>
     <t>IUPAC</t>
   </si>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t>Asm.</t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>CH1.8O0.5N0.2</t>
   </si>
 </sst>
 </file>
@@ -751,17 +757,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC731D4-E3C1-4B64-BF1D-C3C9432561A9}">
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -778,7 +784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -795,7 +801,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -812,7 +818,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -829,7 +835,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -846,7 +852,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -863,7 +869,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -880,7 +886,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -897,7 +903,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -914,7 +920,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -931,7 +937,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -948,7 +954,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -965,7 +971,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -982,7 +988,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -999,7 +1005,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1016,7 +1022,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1033,7 +1039,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1050,7 +1056,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1067,7 +1073,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1084,7 +1090,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1101,7 +1107,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1118,7 +1124,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1135,7 +1141,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1152,7 +1158,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -1169,7 +1175,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1186,7 +1192,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1203,7 +1209,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1220,7 +1226,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -1237,7 +1243,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -1254,7 +1260,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1271,7 +1277,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -1288,7 +1294,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -1305,7 +1311,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>51</v>
       </c>
@@ -1322,7 +1328,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>52</v>
       </c>
@@ -1339,7 +1345,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -1356,7 +1362,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -1373,7 +1379,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>56</v>
       </c>
@@ -1390,7 +1396,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>56</v>
       </c>
@@ -1407,7 +1413,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>58</v>
       </c>
@@ -1424,7 +1430,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>63</v>
       </c>
@@ -1441,7 +1447,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>65</v>
       </c>
@@ -1458,7 +1464,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -1475,7 +1481,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -1492,7 +1498,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -1509,7 +1515,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>75</v>
       </c>
@@ -1526,7 +1532,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>75</v>
       </c>
@@ -1543,7 +1549,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>76</v>
       </c>
@@ -1560,7 +1566,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -1577,7 +1583,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>80</v>
       </c>
@@ -1594,7 +1600,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>81</v>
       </c>
@@ -1611,7 +1617,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>45</v>
       </c>
@@ -1628,7 +1634,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>43</v>
       </c>
@@ -1645,7 +1651,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>86</v>
       </c>
@@ -1660,6 +1666,23 @@
       </c>
       <c r="E53" s="3" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D54" s="3">
+        <v>-91</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
